--- a/reports/finance_report.xlsx
+++ b/reports/finance_report.xlsx
@@ -628,7 +628,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: June 06, 2026</t>
+          <t>Generated: June 10, 2026</t>
         </is>
       </c>
     </row>
